--- a/exports/DF-01_media_checklist.xlsx
+++ b/exports/DF-01_media_checklist.xlsx
@@ -643,7 +643,7 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. Ảnh gồm 3 khung ngang bằng nhau, đánh số 1, 2, 3 to rõ ở góc trên trái mỗi khung; cùng nhân vật, cùng phong cách, chỉ khác ở điểm được hỏi. Ba đồng hồ treo tường: (1) 10:00, (2) 1:00, (3) 11:00.</t>
+          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. Ảnh gồm 3 khung ngang bằng nhau, đánh số 1, 2, 3 to rõ ở góc trên trái mỗi khung; cùng nhân vật, cùng phong cách, chỉ khác ở điểm được hỏi. Ba đồng hồ treo tường giống nhau: (1) 10:00, (2) 10:30, (3) 11:00.</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. Ảnh gồm 3 khung ngang bằng nhau, đánh số 1, 2, 3 to rõ ở góc trên trái mỗi khung; cùng nhân vật, cùng phong cách, chỉ khác ở điểm được hỏi. Khay đồ ăn: (1) hamburger và cốc nước ép, (2) hamburger và tách cà phê, (3) hamburger, khoai tây chiên và cà phê.</t>
+          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. Ảnh gồm 3 khung ngang bằng nhau, đánh số 1, 2, 3 to rõ ở góc trên trái mỗi khung; cùng nhân vật, cùng phong cách, chỉ khác ở điểm được hỏi. Khay đồ ăn: (1) hamburger + cốc nước ép cỡ vừa (M), (2) hamburger + tách cà phê, (3) hamburger + cốc nước ép cỡ nhỏ (S).</t>
         </is>
       </c>
     </row>

--- a/exports/DF-01_media_checklist.xlsx
+++ b/exports/DF-01_media_checklist.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. Ảnh gồm 3 khung ngang bằng nhau, đánh số 1, 2, 3 to rõ ở góc trên trái mỗi khung; cùng nhân vật, cùng phong cách, chỉ khác ở điểm được hỏi. (1) bánh mì và trứng ốp la, (2) bát cơm và cá nướng, (3) đĩa trống bên cạnh tách trà.</t>
+          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. TRANH NGƯỜI NÓI (dải trên cùng): 1 nữ, 1 nam nhân viên văn phòng (chân dung bán thân). 3 TRANH LỰA CHỌN bên dưới: 3 khung ngang bằng nhau, viền đen mảnh, đánh số 1, 2, 3; (1) đĩa bánh mì, trứng ốp la, tách cà phê; (2) bát cơm và cá nướng; (3) một quả chuối.</t>
         </is>
       </c>
     </row>
@@ -573,9 +573,16 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>F：ジョンさん、あさごはんは いつも 何を 食べますか。
-M：パンと たまごです。でも、きょうは 時間が なかったので、何も 食べませんでした。
-F：え、だいじょうぶですか。</t>
+          <t>F：ジョンさん、おはようございます。
+M：あ、おはようございます。
+F：ジョンさんは いつも あさごはんを 食べますか。
+M：はい、毎朝 食べますよ。
+F：何を 食べるんですか。
+M：パンと たまごです。コーヒーも 飲みます。
+F：へえ。ごはんは 食べないんですか。
+M：ごはんは あまり 食べません。でも、きょうは 時間が なくて、何も 食べませんでした。
+F：そうですか。じゃあ、この バナナ、どうぞ。
+M：わあ、ありがとうございます。</t>
         </is>
       </c>
     </row>
@@ -597,7 +604,7 @@
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. Ảnh gồm 3 khung ngang bằng nhau, đánh số 1, 2, 3 to rõ ở góc trên trái mỗi khung; cùng nhân vật, cùng phong cách, chỉ khác ở điểm được hỏi. Cùng một người phụ nữ: (1) chơi tennis, (2) nấu ăn trong bếp, (3) đọc sách trên ghế sofa.</t>
+          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. TRANH NGƯỜI NÓI (dải trên cùng): 1 nam, 1 nữ nhân viên văn phòng. 3 TRANH LỰA CHỌN bên dưới: 3 khung ngang bằng nhau, viền đen mảnh, đánh số 1, 2, 3; (1) người phụ nữ chơi tennis; (2) người phụ nữ làm bánh trong bếp nhà; (3) người phụ nữ cầm hộp bánh đưa cho đồng nghiệp ở văn phòng.</t>
         </is>
       </c>
     </row>
@@ -619,9 +626,14 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>M：やすみの 日は 何を して いますか。
-F：そうですね。前は よく テニスを して いましたが、今は りょうりを するのが すきです。
-M：へえ、いいですね。</t>
+          <t>M：リンさん、休みの 日は 何を して いますか。
+F：そうですね…。前は よく テニスを して いました。
+M：へえ、テニスですか。
+F：ええ。でも、今は 時間が なくて、あまり できません。
+M：そうですか。
+F：最近は 家で 料理を するのが 好きです。週末は いつも ケーキを 作って います。
+M：いいですね。食べて みたいです。
+F：じゃあ、今度 会社に 持って きますね。</t>
         </is>
       </c>
     </row>
@@ -643,7 +655,7 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. Ảnh gồm 3 khung ngang bằng nhau, đánh số 1, 2, 3 to rõ ở góc trên trái mỗi khung; cùng nhân vật, cùng phong cách, chỉ khác ở điểm được hỏi. Ba đồng hồ treo tường giống nhau: (1) 10:00, (2) 10:30, (3) 11:00.</t>
+          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. TRANH NGƯỜI NÓI (dải trên cùng): 1 nữ, 1 nam (bạn bè, đang nói điện thoại hoặc trò chuyện). 3 TRANH LỰA CHỌN bên dưới: 3 khung ngang bằng nhau, viền đen mảnh, đánh số 1, 2, 3; ba đồng hồ treo tường giống nhau chỉ (1) 10:00, (2) 1:00, (3) 12:00.</t>
         </is>
       </c>
     </row>
@@ -666,10 +678,14 @@
       <c r="D11" s="1" t="inlineStr">
         <is>
           <t>F：土曜日、いっしょに 買い物に 行きませんか。
-M：いいですね。何時に しますか。
-F：10時は どうですか。
-M：10時は ちょっと…。11時でも いいですか。
-F：はい、じゃあ 11時に しましょう。</t>
+M：いいですね。行きましょう。
+F：何時に 会いましょうか。
+M：うーん、10時は どうですか。
+F：10時は ちょっと…。12時まで 日本語の クラスが あるんです。
+M：そうですか。じゃあ、1時は？
+F：1時なら だいじょうぶです。
+M：じゃあ、1時に 駅の 前で 会いましょう。
+F：はい、わかりました。</t>
         </is>
       </c>
     </row>
@@ -691,7 +707,7 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. Ảnh gồm 3 khung ngang bằng nhau, đánh số 1, 2, 3 to rõ ở góc trên trái mỗi khung; cùng nhân vật, cùng phong cách, chỉ khác ở điểm được hỏi. Cùng một người đàn ông: (1) tay ôm cổ họng, (2) cầm nhiệt kế, mặt đỏ vì sốt, (3) ôm đầu vì đau đầu.</t>
+          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. TRANH NGƯỜI NÓI (dải trên cùng): 1 nữ, 1 nam nhân viên văn phòng. 3 TRANH LỰA CHỌN bên dưới: 3 khung ngang bằng nhau, viền đen mảnh, đánh số 1, 2, 3; cùng một người đàn ông: (1) tay đặt lên cổ họng, nhăn mặt; (2) cầm nhiệt kế, mặt đỏ; (3) hai tay ôm đầu.</t>
         </is>
       </c>
     </row>
@@ -713,9 +729,14 @@
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>F：どうしたんですか。顔色が わるいですね。
-M：きのうの よるから のどが いたくて…。でも、ねつは ありません。
-F：そうですか。お大事に。</t>
+          <t>F：グエンさん、どうしたんですか。顔色が わるいですね。
+M：ええ、ちょっと…。
+F：かぜですか。
+M：きのうの よるから のどが いたいんです。
+F：ねつは ありますか。
+M：いいえ、ねつは ありません。頭も いたくないです。
+F：そうですか。きょうは 早く 帰った ほうが いいですよ。
+M：はい、そうします。</t>
         </is>
       </c>
     </row>
@@ -737,7 +758,7 @@
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. Ảnh gồm 3 khung ngang bằng nhau, đánh số 1, 2, 3 to rõ ở góc trên trái mỗi khung; cùng nhân vật, cùng phong cách, chỉ khác ở điểm được hỏi. Khay đồ ăn: (1) hamburger + cốc nước ép cỡ vừa (M), (2) hamburger + tách cà phê, (3) hamburger + cốc nước ép cỡ nhỏ (S).</t>
+          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. TRANH NGƯỜI NÓI (dải trên cùng): khách nam đứng trước quầy, nhân viên nữ sau quầy thu ngân. 3 TRANH LỰA CHỌN bên dưới: 3 khung ngang bằng nhau, viền đen mảnh, đánh số 1, 2, 3; chỉ vẽ đồ vật trên khay: (1) hamburger + cốc nước cam cỡ vừa; (2) hamburger + cốc cà phê cỡ vừa; (3) hamburger + cốc nước cam cỡ nhỏ.</t>
         </is>
       </c>
     </row>
@@ -759,11 +780,16 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>F：いらっしゃいませ。ごちゅうもんは？
-M：ハンバーガーと ジュースを ください。
-F：ジュースは Sと Mが ありますが。
-M：Mで おねがいします。あ、すみません。ジュースじゃなくて、コーヒーに して ください。
-F：はい、かしこまりました。</t>
+          <t>F：いらっしゃいませ。ご注文は？
+M：ハンバーガーを 一つ ください。
+F：はい。お飲み物は いかがですか。
+M：じゃあ、オレンジジュースを。
+F：サイズは Sと Mが ありますが。
+M：Mで お願いします。
+F：かしこまりました。ハンバーガーと オレンジジュースの Mですね。
+M：あ、すみません。やっぱり ジュースじゃなくて、コーヒーに して ください。
+F：はい、ホットコーヒーですね。サイズは Mで よろしいですか。
+M：はい、お願いします。</t>
         </is>
       </c>
     </row>
@@ -785,7 +811,7 @@
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. Ảnh gồm 3 khung ngang bằng nhau, đánh số 1, 2, 3 to rõ ở góc trên trái mỗi khung; cùng nhân vật, cùng phong cách, chỉ khác ở điểm được hỏi. Ba bản đồ đơn giản giống nhau (ngân hàng ở góc, siêu thị), dấu bưu điện ở: (1) rẽ trái ở góc ngân hàng, cạnh siêu thị, (2) rẽ phải ở góc ngân hàng, (3) đi thẳng qua ngân hàng.</t>
+          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. TRANH NGƯỜI NÓI (dải trên cùng): người đàn ông hỏi đường một người phụ nữ trên phố. 3 TRANH LỰA CHỌN bên dưới: 3 khung ngang bằng nhau, viền đen mảnh, đánh số 1, 2, 3; ba bản đồ đơn giản giống nhau (đường thẳng, ngân hàng ở góc, siêu thị, bệnh viện), dấu ngôi sao bưu điện ở: (1) rẽ trái ở góc ngân hàng, cạnh siêu thị; (2) rẽ phải ở góc ngân hàng; (3) đi thẳng qua ngân hàng, cạnh bệnh viện. Không ghi chữ, dùng biểu tượng.</t>
         </is>
       </c>
     </row>
@@ -807,9 +833,13 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>M：すみません、ゆうびんきょくは どこですか。
-F：この 道を まっすぐ 行って、銀行の かどを 左に まがって ください。ゆうびんきょくは スーパーの となりですよ。
-M：ありがとうございます。</t>
+          <t>M：すみません。この 近くに ゆうびんきょくは ありますか。
+F：ゆうびんきょくですか。ええと、この 道を まっすぐ 行って ください。
+M：まっすぐですね。
+F：はい。それから、銀行の かどを 左に まがって ください。
+M：銀行の かどを 左…。
+F：ええ。ゆうびんきょくは スーパーの となりに ありますよ。
+M：スーパーの となりですね。わかりました。ありがとうございます。</t>
         </is>
       </c>
     </row>
@@ -831,7 +861,7 @@
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. Ảnh gồm 3 khung ngang bằng nhau, đánh số 1, 2, 3 to rõ ở góc trên trái mỗi khung; cùng nhân vật, cùng phong cách, chỉ khác ở điểm được hỏi. (1) người nằm trên giường chuẩn bị ngủ, cầm thuốc, (2) uống thuốc trước bữa ăn (bàn ăn còn đầy), (3) uống thuốc sau bữa ăn (bát đĩa đã trống).</t>
+          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. TRANH NGƯỜI NÓI (dải trên cùng): dược sĩ nữ sau quầy hiệu thuốc, khách nam. 3 TRANH LỰA CHỌN bên dưới: 3 khung ngang bằng nhau, viền đen mảnh, đánh số 1, 2, 3; (1) người đàn ông ngồi trên giường uống thuốc, đồng hồ chỉ đêm; (2) uống thuốc trước bàn ăn còn đầy thức ăn; (3) uống thuốc bên bàn ăn đã ăn xong, bát đĩa trống.</t>
         </is>
       </c>
     </row>
@@ -853,9 +883,14 @@
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>F：この くすりは 1日 3回、ごはんを 食べた あとで 飲んで ください。
+          <t>F：お待たせしました。こちらが かぜの くすりです。
+M：はい。
+F：1日 3回、ごはんを 食べた あとで 飲んで ください。
+M：ごはんの 前じゃ ないんですね。
+F：はい、食べた あとです。
 M：ねる 前にも 飲みますか。
-F：いいえ、ねる 前は 飲まないで ください。</t>
+F：いいえ、ねる 前は 飲まないで ください。
+M：わかりました。ありがとうございます。</t>
         </is>
       </c>
     </row>
@@ -877,7 +912,7 @@
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. Ảnh gồm 3 khung ngang bằng nhau, đánh số 1, 2, 3 to rõ ở góc trên trái mỗi khung; cùng nhân vật, cùng phong cách, chỉ khác ở điểm được hỏi. Cùng một người phụ nữ sau khi cắt: (1) mái ngắn, phía sau vẫn dài, (2) cả mái và phía sau đều ngắn, (3) mái dài, phía sau ngắn.</t>
+          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. TRANH NGƯỜI NÓI (dải trên cùng): thợ cắt tóc nam đứng sau, khách nữ ngồi ghế. 3 TRANH LỰA CHỌN bên dưới: 3 khung ngang bằng nhau, viền đen mảnh, đánh số 1, 2, 3; cùng một người phụ nữ sau khi cắt: (1) mái ngắn ngang trên mắt, tóc sau dài qua vai; (2) mái ngắn, tóc sau ngắn; (3) mái dài che mắt, tóc sau ngắn.</t>
         </is>
       </c>
     </row>
@@ -899,9 +934,13 @@
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>M：きょうは どう しますか。
-F：前髪は 短く して ください。うしろは あまり 切らないで ください。
-M：はい、わかりました。</t>
+          <t>M：いらっしゃいませ。きょうは どう しますか。
+F：前髪を 短く して ください。
+M：はい。どのぐらい 切りますか。
+F：目の 上ぐらいまで お願いします。
+M：うしろは どう しますか。
+F：うしろは 長いままが いいです。少しだけ そろえて ください。
+M：わかりました。</t>
         </is>
       </c>
     </row>
@@ -923,7 +962,7 @@
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. Ảnh gồm 3 khung ngang bằng nhau, đánh số 1, 2, 3 to rõ ở góc trên trái mỗi khung; cùng nhân vật, cùng phong cách, chỉ khác ở điểm được hỏi. Ba bảng số: (1) 10分, (2) 20分, (3) 30分 – vẽ như mặt đồng hồ đếm ngược, không có chữ khác.</t>
+          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. TRANH NGƯỜI NÓI (dải trên cùng): một nhân viên nhà ga nữ (đồng phục, mũ) cầm micro. 3 TRANH LỰA CHỌN bên dưới: 3 khung ngang bằng nhau, viền đen mảnh, đánh số 1, 2, 3; kiểu biểu tượng xám đơn giản: ba đồng hồ, kim phút chỉ khoảng chờ 10 / 20 / 30 phút (vẽ cung tô màu trên mặt đồng hồ, không chữ).</t>
         </is>
       </c>
     </row>
@@ -945,8 +984,7 @@
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>N：駅の アナウンスです。
-F：お客さまに おしらせします。さくら駅で じこが あったので、電車が 20分 おくれて います。また、きょうは 3番線ではなく、5番線から 出発します。ご注意ください。</t>
+          <t>F：お客さまに おしらせします。さくら駅で じこが あったので、電車が 20分ぐらい おくれて います。ご迷惑を おかけして、もうしわけ ございません。また、つぎの 東京行きの 電車は、いつもの 3番線ではなく、5番線から 出発します。5番線の 電車に お乗りください。くりかえします。東京行きの 電車は、5番線から 出発します。</t>
         </is>
       </c>
     </row>
@@ -968,7 +1006,7 @@
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. Ảnh gồm 3 khung ngang bằng nhau, đánh số 1, 2, 3 to rõ ở góc trên trái mỗi khung; cùng nhân vật, cùng phong cách, chỉ khác ở điểm được hỏi. Ba biển sân ga: (1) số 5, (2) số 3, (3) số 7.</t>
+          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. 3 TRANH LỰA CHỌN bên dưới: 3 khung ngang bằng nhau, viền đen mảnh, đánh số 1, 2, 3; kiểu biểu tượng xám đơn giản: ba biển sân ga có đoàn tàu, mỗi biển chỉ ghi một chữ số lớn (1) 5, (2) 3, (3) 7.</t>
         </is>
       </c>
     </row>
@@ -990,7 +1028,7 @@
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. Ảnh gồm 3 khung ngang bằng nhau, đánh số 1, 2, 3 to rõ ở góc trên trái mỗi khung; cùng nhân vật, cùng phong cách, chỉ khác ở điểm được hỏi. Văn phòng khi động đất: (1) người chạy ra cửa, (2) người bấm thang máy, (3) người chui xuống gầm bàn.</t>
+          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. TRANH NGƯỜI NÓI (dải trên cùng): một người phụ trách nam mặc áo công ty, đứng nói. 3 TRANH LỰA CHỌN bên dưới: 3 khung ngang bằng nhau, viền đen mảnh, đánh số 1, 2, 3; kiểu biểu tượng xám (pictogram) như biển báo: (1) người chạy ra cửa; (2) người chui dưới gầm bàn, tay che đầu; (3) người đứng trong thang máy.</t>
         </is>
       </c>
     </row>
@@ -1012,8 +1050,7 @@
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>N：会社で、地震の ときの 説明を して います。
-M：地震が きたら、まず 机の 下に 入って ください。ゆれて いる あいだは、外に 出ないで ください。ゆれが 止まったら、エレベーターは 使わないで、かいだんで 1階に おりて ください。</t>
+          <t>M：みなさん、きょうは 地震の ときの 訓練を します。よく 聞いて ください。地震が 起きたら、まず 机の 下に 入って、頭を 守って ください。ゆれて いる あいだは、外に 出ないで ください。ゆれが 止まったら、エレベーターは 使わないで、かいだんで 1階まで おりて ください。そのあと、会社の 前の 公園に 集まって ください。駐車場には 行かないで ください。</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1072,7 @@
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. Ảnh gồm 3 khung ngang bằng nhau, đánh số 1, 2, 3 to rõ ở góc trên trái mỗi khung; cùng nhân vật, cùng phong cách, chỉ khác ở điểm được hỏi. (1) người đi xuống cầu thang bộ, (2) người đứng trong thang máy, (3) người trèo qua cửa sổ.</t>
+          <t>Tranh minh hoạ phẳng, nét đen mảnh, màu pastel nhẹ, nền trắng, bối cảnh Nhật Bản, không có chữ. 3 TRANH LỰA CHỌN bên dưới: 3 khung ngang bằng nhau, viền đen mảnh, đánh số 1, 2, 3; kiểu biểu tượng xám/màu nhạt: (1) sảnh tầng 1 trong toà nhà; (2) bãi đỗ xe có ô tô; (3) công viên có cây và cầu trượt, phía sau là toà nhà công ty.</t>
         </is>
       </c>
     </row>

--- a/exports/DF-01_media_checklist.xlsx
+++ b/exports/DF-01_media_checklist.xlsx
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>M：みなさん、きょうは 地震の ときの 訓練を します。よく 聞いて ください。地震が 起きたら、まず 机の 下に 入って、頭を 守って ください。ゆれて いる あいだは、外に 出ないで ください。ゆれが 止まったら、エレベーターは 使わないで、かいだんで 1階まで おりて ください。そのあと、会社の 前の 公園に 集まって ください。駐車場には 行かないで ください。</t>
+          <t>M：では、これから 地震の ときに どう するかに ついて お話しします。地震が 起きたら、まず 机の 下に 入って、頭を 守って ください。ゆれて いる あいだは、外に 出ないで ください。ゆれが 止まったら、エレベーターは 使わないで、かいだんで 1階まで おりて ください。そのあと、会社の 前の 公園に 集まって ください。駐車場で ほかの 人を 待ったり しないで、できるだけ 早く 公園に 行って ください。わたしからの 説明は 以上です。</t>
         </is>
       </c>
     </row>
